--- a/Employee_Reports_wi52/Ray Maitem Maureal Q0477.xlsx
+++ b/Employee_Reports_wi52/Ray Maitem Maureal Q0477.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -745,40 +745,28 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FMC-deck (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-M-005</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>EQUIPMENT MANUAL</t>
-        </is>
-      </c>
+          <t>BB TV 20FT (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>27-Oct-2024</t>
+          <t>19-Aug-2026</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>27-Oct-2026</t>
+          <t>18-Aug-2028</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>68</v>
+        <v>721</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -794,40 +782,28 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Weight scales (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-M-013</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>EQUIPMENT MANUAL</t>
-        </is>
-      </c>
+          <t>BB TV 15FT (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>15-Feb-2025</t>
+          <t>19-Aug-2026</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>15-Feb-2027</t>
+          <t>18-Aug-2028</t>
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>179</v>
+        <v>721</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -843,7 +819,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Tilting deck (Cargo Trainings)</t>
+          <t>FMC-deck (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -853,7 +829,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-009</t>
+          <t>LSME-CRG-M-005</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -863,20 +839,20 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>09-Mar-2025</t>
+          <t>27-Oct-2024</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>09-Mar-2027</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -892,7 +868,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>TT+RA (Cargo Trainings)</t>
+          <t>Weight scales (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -902,7 +878,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-007</t>
+          <t>LSME-CRG-M-013</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -912,20 +888,20 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>18-Aug-2026</t>
+          <t>19-Aug-2026</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>17-Aug-2028</t>
+          <t>18-Aug-2028</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -941,7 +917,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>CS-Hoist (Cargo Trainings)</t>
+          <t>Tilting deck (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -951,7 +927,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-001</t>
+          <t>LSME-CRG-M-009</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -961,20 +937,20 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>09-Mar-2025</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>18-Aug-2028</t>
+          <t>09-Mar-2027</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>729</v>
+        <v>193</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -990,7 +966,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>ULD Hoist (Cargo Trainings)</t>
+          <t>TT+RA (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1000,7 +976,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-008</t>
+          <t>LSME-CRG-M-007</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1010,20 +986,20 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>31-Aug-2025</t>
+          <t>18-Aug-2026</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>31-Aug-2027</t>
+          <t>17-Aug-2028</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>376</v>
+        <v>720</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1039,7 +1015,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Truck dock (Cargo Trainings)</t>
+          <t>CS-Hoist (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1049,7 +1025,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-006</t>
+          <t>LSME-CRG-M-001</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1059,20 +1035,20 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>07-Dec-2024</t>
+          <t>19-Aug-2026</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>07-Dec-2026</t>
+          <t>18-Aug-2028</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>109</v>
+        <v>721</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1083,53 +1059,53 @@
       <c r="K13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Softwares &amp; Param. (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>ULD Hoist (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>LSME-CRG-M-018</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-008</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>01-Sep-2024</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>01-Sep-2026</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>31-Aug-2025</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>31-Aug-2027</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>368</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1137,146 +1113,146 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>Truck dock (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-006</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>07-Dec-2024</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>07-Dec-2026</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Softwares &amp; Param. (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-018</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>01-Sep-2024</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>01-Sep-2026</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>Control circuits (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-M-019</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>03-May-2028</t>
         </is>
       </c>
-      <c r="H15" s="3" t="n">
-        <v>622</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Cool Room (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>LSME-CRG-M-011</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>EQUIPMENT MANUAL</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>10-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Climate Control Center (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>LSME-CRG-M-014</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>EQUIPMENT MANUAL</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>12-Sep-2024</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>12-Sep-2026</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="H17" s="3" t="n">
+        <v>614</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1284,7 +1260,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>3TIER RACK -G/H/A/303 (Cargo Trainings)</t>
+          <t>Cool Room (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1294,7 +1270,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-015</t>
+          <t>LSME-CRG-M-011</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1304,20 +1280,20 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>20-Aug-2026</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>03-May-2028</t>
+          <t>19-Aug-2028</t>
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>622</v>
+        <v>722</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1328,53 +1304,53 @@
       <c r="K18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>3TIER RACK -JBAY (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Climate Control Center (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-M-017</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-014</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>03-May-2028</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>622</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>12-Sep-2024</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>12-Sep-2026</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1382,7 +1358,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Non-powered roller Decks (Cargo Trainings)</t>
+          <t>3TIER RACK -G/H/A/303 (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1392,7 +1368,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-016</t>
+          <t>LSME-CRG-M-015</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1402,20 +1378,20 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>01-Feb-2025</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>01-Feb-2027</t>
+          <t>03-May-2028</t>
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>165</v>
+        <v>614</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1426,53 +1402,53 @@
       <c r="K20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Lodige LOTO Procedure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>ELECTRICAL SAFETY</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>LSME-OHS-SOP-021</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>03-Nov-2024</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>03-Nov-2025</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>-290</v>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>3TIER RACK -JBAY (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-017</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>03-May-2028</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>614</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1480,8 +1456,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Equipment Operation Procedure
-(SOP-031) (SOPs)</t>
+          <t>Non-powered roller Decks (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1491,87 +1466,87 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-031</t>
+          <t>LSME-CRG-M-016</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>01-Feb-2025</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>01-Feb-2027</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Lodige LOTO Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>ELECTRICAL SAFETY</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>LSME-OHS-SOP-021</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>03-Apr-2026</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>03-Apr-2027</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>226</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-028</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>03-Apr-2026</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>03-Apr-2027</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>226</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>03-Nov-2024</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>03-Nov-2025</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>-298</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1579,7 +1554,8 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>STACKER CRANE AISLE MONTHLY PREVENTIVE MAINTENANCE (SOPs)</t>
+          <t>Equipment Operation Procedure
+(SOP-031) (SOPs)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1589,7 +1565,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-035</t>
+          <t>LSME-CRG-SOP-031</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1599,20 +1575,20 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>22-Dec-2025</t>
+          <t>03-Apr-2026</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>22-Dec-2026</t>
+          <t>03-Apr-2027</t>
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>124</v>
+        <v>218</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1623,41 +1599,53 @@
       <c r="K24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Endangered by Electricity A safety Training (SOPs)</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>26-Sep-2025</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>26-Sep-2026</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-028</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>03-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>03-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1665,244 +1653,232 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>STACKER CRANE AISLE MONTHLY PREVENTIVE MAINTENANCE (SOPs)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-035</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>22-Dec-2025</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>22-Dec-2026</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Endangered by Electricity A safety Training (SOPs)</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>26-Sep-2025</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>26-Sep-2026</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
           <t>Incident Escalation Process(LSME-IMS-SOP-021 ) (SOPs)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-021</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>20-Feb-2026</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>20-Feb-2027</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>184</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="H28" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Misaligned Pallet-ULD Recovery Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-030</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>03-Apr-2026</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>03-Apr-2027</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n">
-        <v>226</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="H29" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-018</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>18-Mar-2025</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>18-Mar-2026</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
-        <v>-155</v>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="H30" s="4" t="n">
+        <v>-163</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>IMS</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>LSME-IMS-SOP-022</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>10-Apr-2025</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>10-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>-132</v>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-041</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>21-May-2026</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>21-May-2027</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1910,146 +1886,146 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
+          <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>10-Apr-2025</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>10-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>-140</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-041</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2027</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
           <t>Stacker Crane Aisle Annual Maintenance And Megger Test Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-003</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>29-Jul-2025</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>29-Jul-2026</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Weight Scale Verification Procedure(LSME-IMS-SOP-023 ) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>IMS</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>LSME-IMS-SOP-023</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>18-Jul-2025</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>18-Jul-2026</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>-33</v>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Replacement of Stacker Crane Driven Wheel (SOPs)</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-009</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>27-Jul-2025</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>27-Jul-2026</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>21-Aug-2027</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>358</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2057,257 +2033,281 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
+          <t>Weight Scale Verification Procedure(LSME-IMS-SOP-023 ) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-023</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>18-Jul-2025</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>18-Jul-2026</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Replacement of Stacker Crane Driven Wheel (SOPs)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-009</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>21-Aug-2027</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>358</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
           <t>Replacement of Stacker Crane Fork Flyer Chain (SOPs)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-010</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>27-Jul-2025</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>27-Jul-2026</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>22-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>22-Aug-2027</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>359</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Replacement of Stacker Crane Wire Rope (SOPs)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>27-Jul-2025</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>27-Jul-2026</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>22-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>22-Aug-2027</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>359</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-011</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>31-Aug-2025</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>31-Aug-2026</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="H38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Overload and Load Testing Procedure In ULD Hoist (SOPs)</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-018</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>31-Aug-2025</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>31-Aug-2026</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="H39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>ULD Hoist Drve Motor Replacement (SOPs)</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>24-Nov-2025</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>24-Nov-2026</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>EOP For ULD System Failure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>15-Jun-2026</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>15-Jun-2027</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>EOP For CS System Failure (SOPs)</t>
+          <t>ULD Hoist Drve Motor Replacement (SOPs)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr"/>
@@ -2323,20 +2323,20 @@
       <c r="E40" s="3" t="inlineStr"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>24-Nov-2025</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>15-Jun-2027</t>
+          <t>24-Nov-2026</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>299</v>
+        <v>88</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>EOP For Cold Storage System due to Equipment Failure (SOPs)</t>
+          <t>EOP For ULD System Failure (SOPs)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
@@ -2369,11 +2369,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2389,40 +2389,28 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Equipment Teaching Procedure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-027</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
+          <t>EOP For CS System Failure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>09-Jan-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>09-Jan-2027</t>
+          <t>15-Jun-2027</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>142</v>
+        <v>291</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2438,7 +2426,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>IS0 55001 (Other Trainings)</t>
+          <t>EOP For Cold Storage System due to Equipment Failure (SOPs)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
@@ -2446,28 +2434,114 @@
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>15-Jun-2027</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Equipment Teaching Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-027</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>09-Jan-2026</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>09-Jan-2027</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
           <t>01-Jul-2025</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>01-Jul-2027</t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
-        <v>315</v>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3067,7 +3141,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3096,7 +3170,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7926</v>
+        <v>7918</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3125,7 +3199,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3154,7 +3228,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7926</v>
+        <v>7918</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3183,7 +3257,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3278,7 +3352,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7958</v>
+        <v>7950</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3307,7 +3381,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7973</v>
+        <v>7965</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3336,7 +3410,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7958</v>
+        <v>7950</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3365,7 +3439,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3394,7 +3468,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3423,7 +3497,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7919</v>
+        <v>7911</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3452,7 +3526,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3481,7 +3555,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7917</v>
+        <v>7909</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3510,7 +3584,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3539,7 +3613,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7919</v>
+        <v>7911</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3568,7 +3642,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3597,7 +3671,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3626,7 +3700,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7931</v>
+        <v>7923</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3655,7 +3729,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7931</v>
+        <v>7923</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3684,7 +3758,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7912</v>
+        <v>7904</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3713,7 +3787,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7973</v>
+        <v>7965</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3742,7 +3816,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3771,7 +3845,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7917</v>
+        <v>7909</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3800,7 +3874,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7993</v>
+        <v>7985</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3829,7 +3903,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7940</v>
+        <v>7932</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3858,7 +3932,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7940</v>
+        <v>7932</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -3887,7 +3961,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>7993</v>
+        <v>7985</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -3916,7 +3990,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>7912</v>
+        <v>7904</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -3945,7 +4019,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -3974,7 +4048,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>7993</v>
+        <v>7985</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
